--- a/AAII_Financials/Quarterly/BBUC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBUC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>BBUC</t>
   </si>
@@ -656,354 +656,367 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6497000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6436000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7094000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6919000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6695000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6749000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7427000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9232000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1929000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1865000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1946000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1964000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1908000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1865000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4244000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3986200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3136700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3096300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3360500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3159000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6666000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3275600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3127600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6173700</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5224000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5126000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5584000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5663000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5465000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5402000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5965000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7069000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1860000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1652000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1749000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1760000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1669000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1616000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3704600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3573200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2855300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2785400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2964800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2918700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6144700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3007400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2640400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5349300</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1273000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1310000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1510000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1256000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1230000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1347000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1462000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2163000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>69000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>213000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>197000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>204000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>239000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>249000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>539300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>413000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>281500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>310900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>395800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>240300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>521300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>268200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>487200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>824400</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1031,8 +1044,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1108,8 +1122,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1185,67 +1202,70 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-35000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>163000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>53000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>87000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-101000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1319000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-533000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-37000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>514000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>46000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-256000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>17700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>26100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1253,62 +1273,65 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-72400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>775000</v>
+      </c>
+      <c r="E15" s="3">
         <v>760000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>142000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>772000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>767000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>730000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>129000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>808000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>194000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>196000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>163000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>249000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>272000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>282000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1331,16 +1354,19 @@
         <v>0</v>
       </c>
       <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
         <v>186100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>378300</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1365,162 +1391,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5513000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5422000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5912000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5941000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5736000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5713000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6332000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7388000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1937000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1716000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1827000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1826000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1732000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1677000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3862200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3776300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2958100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2878900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3053900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3018600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6341100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3093100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2862700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5932400</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>984000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1014000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1182000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>978000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>959000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1036000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1095000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1844000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>149000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>119000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>138000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>176000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>188000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>381700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>209900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>178600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>217300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>306600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>140400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>324900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>182500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>264900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>241300</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1548,209 +1581,216 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>59000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>296000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-22000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>168000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-143000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>121000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>431000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-144000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-98000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>161000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-187500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-196200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>737500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-436000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-185000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-166100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-311100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-120300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-227500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-405700</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1704000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1779000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1265000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1454000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1725000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1788000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1227000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2484000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>329000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>224000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-149000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>531000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>546000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>309000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>576000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>433600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1127200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-13800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>326900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>793500</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>739000</v>
+      </c>
+      <c r="E22" s="3">
         <v>766000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>784000</v>
       </c>
       <c r="F22" s="3">
         <v>784000</v>
       </c>
       <c r="G22" s="3">
+        <v>784000</v>
+      </c>
+      <c r="H22" s="3">
         <v>801000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>770000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>752000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>778000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>203000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>210000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>206000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>227000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>233000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>212000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1779,162 +1819,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E23" s="3">
         <v>288000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>176000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-155000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>70000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>389000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-973000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1431000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-184000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1032000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>297000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-185000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>194300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>916100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-218700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>121600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-25700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>13800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>62200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>37500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-164400</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E24" s="3">
         <v>72000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>58000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-33000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-65000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>133000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>135000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-304000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-71000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-31000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>102000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-20400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-28800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-504700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-41900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>23500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-23500</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2010,162 +2059,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E26" s="3">
         <v>216000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>118000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-122000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>135000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>256000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1108000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1735000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>40000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-174000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1036000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>40000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>195000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-182000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>214600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>42500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1420900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-224200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>163400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-28400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>49800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-140900</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E27" s="3">
         <v>40000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-42000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25000</v>
       </c>
-      <c r="G27" s="3">
-        <v>11000</v>
-      </c>
       <c r="H27" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I27" s="3">
         <v>80000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-150000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>103000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>124000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-150000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>454000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>97000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>108000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>263500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>126200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1067700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-225600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>48600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-186500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2241,8 +2299,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2274,28 +2335,28 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>3885000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-33000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-37000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2318,8 +2379,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2395,8 +2459,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2472,162 +2539,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-59000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-296000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>22000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-168000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>143000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-121000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-431000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>144000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>98000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>187500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>196200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-737500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>436000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>185000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>166100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>311100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>120300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>227500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>405700</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E33" s="3">
         <v>40000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-42000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25000</v>
       </c>
-      <c r="G33" s="3">
-        <v>11000</v>
-      </c>
       <c r="H33" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I33" s="3">
         <v>80000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-150000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>103000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>124000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-150000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>454000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>97000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>108000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>263500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>126200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1067700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-225600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>48600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>15200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-186500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2703,167 +2779,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E35" s="3">
         <v>40000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-42000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25000</v>
       </c>
-      <c r="G35" s="3">
-        <v>11000</v>
-      </c>
       <c r="H35" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I35" s="3">
         <v>80000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-150000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>103000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>124000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-150000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>454000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>97000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>108000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>263500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>126200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1067700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-225600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>48600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>15200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-186500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2891,8 +2976,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2920,71 +3006,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3447000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4524000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3546000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3500000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3329000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3442000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3239000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3003000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>754000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>743000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>772000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>646000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>836000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>810000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>999900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1211700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1120400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>917500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1207500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1119200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,52 +3084,55 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>667000</v>
+      </c>
+      <c r="E42" s="3">
         <v>732000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>724000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>910000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>838000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>790000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>791000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>707000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>41000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -3050,8 +3140,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3074,71 +3164,74 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6635000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6577000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6996000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7240000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6606000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6562000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5744000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5971000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1531000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1692000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1519000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2640000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2561000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3061000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3131300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2428800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2997300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2808800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2165200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2122200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3151,71 +3244,74 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2827000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2651000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2562000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2667000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2870000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2740000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2416000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2730000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>63000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>59000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>704000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>706000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>655000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>862600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>823300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>832200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>799200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>783400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>793800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,71 +3324,74 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4454000</v>
+      </c>
+      <c r="E45" s="3">
         <v>369000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>261000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>267000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1340000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>650000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2227000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>637000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>558000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1635600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1735800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2163800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1115500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1065700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1026000</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,71 +3404,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19029000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15825000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15043000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15516000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15893000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15050000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15339000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14227000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2755000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2876000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2751000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4554000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4685000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5570000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6629500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6199600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7113800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5640900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5221800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5061200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,71 +3484,74 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7978000</v>
+      </c>
+      <c r="E47" s="3">
         <v>7707000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7770000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7470000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7000000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6955000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7025000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7431000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>218000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>226000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>231000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>249000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>265000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>262000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1577200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1531400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1106900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1261300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1021100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1036800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,71 +3564,74 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9343000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11244000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11013000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10810000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10591000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12529000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13232000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15527000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2671000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2622000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2743000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3607000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3750000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3731000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5114800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4854800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5119200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5607900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5451400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5355500</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,71 +3644,74 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31186000</v>
+      </c>
+      <c r="E49" s="3">
         <v>31536000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>31823000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32167000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32445000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>32189000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>30556000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>32874000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12111000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12406000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12633000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15558000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15794000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15665000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22019900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22054000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9634800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9446900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8701200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8708900</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3613,8 +3724,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3690,8 +3804,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3767,71 +3884,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>745000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1240000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1477000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1299000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1279000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1382000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1192000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>752000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>520000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>527000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>601000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>977000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>955000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>883000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1848900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1864800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1613000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1217300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1107600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1028700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,8 +3964,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3921,71 +4044,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78820000</v>
+      </c>
+      <c r="E54" s="3">
         <v>77056000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75761000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>75403000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>75335000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75887000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75474000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>80256000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20503000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20887000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21182000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26345000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26926000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27578000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37190300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>36504600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24587600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23174400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21503100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21191000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4124,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4027,8 +4156,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4056,71 +4186,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3394000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3318000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3456000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3447000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3380000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3358000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3250000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3657000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>868000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>833000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>849000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1118000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1227000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1207000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1702200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1598600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1740200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1899600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1837000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1741500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4133,71 +4264,74 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2179000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1830000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1565000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1479000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1571000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1637000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1834000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2315000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>275000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>340000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>900000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1581000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1568000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>986000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>976800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>731400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>665800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>371400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2675700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>187700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4210,71 +4344,74 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4666000</v>
+      </c>
+      <c r="E59" s="3">
         <v>864000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>835000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>915000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1607000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1827000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3298000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1699000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2514000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2743000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2534000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3039000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3237000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3224000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5451700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5479200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5292400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6343800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3090400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3137400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4287,71 +4424,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13248000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11076000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8982000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9098000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9545000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10147000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12166000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12159000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4407000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4651000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4828000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6672000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6900000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6278000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8130600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7809200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7698400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8614800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7603100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5066600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4364,71 +4504,74 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43503000</v>
+      </c>
+      <c r="E61" s="3">
         <v>43772000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>43008000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>42644000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42860000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42717000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37975000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40232000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8341000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8495000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9580000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13351000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13529000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14556000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>17553200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18073200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10567100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8199400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7555800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7457400</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4441,71 +4584,74 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4056000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3984000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5728000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5304000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4715000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5313000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5178000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5320000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1962000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1938000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>714000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>882000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>960000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>944000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5976000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6288800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4519700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5044000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4809800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5178600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4518,8 +4664,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4595,8 +4744,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4672,8 +4824,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4749,71 +4904,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63381000</v>
+      </c>
+      <c r="E66" s="3">
         <v>61536000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60450000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59863000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60014000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61032000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58166000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>60895000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15921000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16331000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16422000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22670000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23226000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23692000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36702600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36324900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>24511900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>24100100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22200100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19561500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4826,8 +4984,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4855,8 +5016,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4932,8 +5094,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5009,8 +5174,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5086,8 +5254,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5163,53 +5334,56 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1336000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1313000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>413000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>463000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>509000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>516000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>491000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>648000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>622000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>498000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>637000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>183000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>86000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
@@ -5240,8 +5414,11 @@
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5317,8 +5494,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5394,8 +5574,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5471,71 +5654,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5431000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5480000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2294000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2354000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2291000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2158000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1752000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1980000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>849000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>722000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>880000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>404000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>327000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>192000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>487700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>179800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-925700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-697000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1629500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5548,8 +5734,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5625,167 +5814,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E81" s="3">
         <v>40000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-42000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25000</v>
       </c>
-      <c r="G81" s="3">
-        <v>11000</v>
-      </c>
       <c r="H81" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I81" s="3">
         <v>80000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-150000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>103000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>124000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-150000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>454000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>97000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>108000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>263500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>126200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1067700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-225600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>48600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>15200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-186500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5813,85 +6011,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>767000</v>
+      </c>
+      <c r="E83" s="3">
         <v>730000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>388000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>808000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>809000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>808000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>412000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>894000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>282000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>306000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>156000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>149000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>381700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>419900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>211100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>204900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>205300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3">
         <v>756100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5967,8 +6169,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6044,8 +6249,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6121,8 +6329,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6198,8 +6409,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6275,85 +6489,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>765000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>632000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1300000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>483000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>815000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>948000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1910000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>34000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-53000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>181000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>164400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-186600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>219200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>46800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>245800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3">
         <v>664300</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6381,85 +6601,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-722000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-489000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-554000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-537000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-475000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-494000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-596000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-667000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-78000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-76000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-130000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-171000</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-173000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-216000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-166000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-129000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-144000</v>
       </c>
       <c r="U91" s="3">
         <v>-144000</v>
       </c>
       <c r="V91" s="3">
+        <v>-144000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-507000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-616500</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6535,8 +6759,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6612,85 +6839,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1535000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-465000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-843000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-401000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-485000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1454000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-352000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-891000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-94000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-77000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3580000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-168000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>110000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-292100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10061000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2094800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-185700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-204000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-303700</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6718,65 +6951,66 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
         <v>13000</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="E96" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3">
         <v>12000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>14000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>13000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3">
         <v>14000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>4000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>5000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>4000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>5000</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3">
         <v>5000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-5500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>102800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-111400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -6795,8 +7029,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6872,8 +7109,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6949,8 +7189,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7026,235 +7269,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>890000</v>
+      </c>
+      <c r="E100" s="3">
         <v>625000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>283000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-744000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-224000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>757000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-48000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-987000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>110000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>124000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3660000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-27000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>89000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-118200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10372500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2159700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-213200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>55400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-378700</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E101" s="3">
         <v>88000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-223000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>62000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-94000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-68000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>80000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-64000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>15000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-36000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-49000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>29000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>46200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-49400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-66300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>39900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9500</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-635000</v>
+      </c>
+      <c r="E102" s="3">
         <v>978000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>171000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-101000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>206000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>325000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>94000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>126000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-190000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>74000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-199700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>75500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>217900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-312200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>87800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
